--- a/other/backup_request_form.xlsx
+++ b/other/backup_request_form.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'file_type',_'label':_'document',_'value':_'document'}</t>
+          <t>document</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'file_type', 'label': 'Document', 'value': 'Document'}</t>
+          <t>Document</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'file_type',_'label':_'image',_'value':_'image'}</t>
+          <t>image</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'file_type', 'label': 'Image', 'value': 'Image'}</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'backup_location',_'label':_'server',_'value':_'server'}</t>
+          <t>server</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'backup_location', 'label': 'Server', 'value': 'Server'}</t>
+          <t>Server</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'backup_location',_'label':_'cloud',_'value':_'cloud'}</t>
+          <t>cloud</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'backup_location', 'label': 'Cloud', 'value': 'Cloud'}</t>
+          <t>Cloud</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'file_status',_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'file_status', 'label': 'Pending', 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'file_status',_'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'file_status', 'label': 'Completed', 'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'file_status',_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'file_status', 'label': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'backup_status',_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'backup_status', 'label': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'backup_status',_'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'backup_status', 'label': 'Completed', 'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_started',_'label':_'not_started',_'value':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Started', 'label': 'Not Started', 'value': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'request_type',_'label':_'backup',_'value':_'backup'}</t>
+          <t>backup</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'request_type', 'label': 'Backup', 'value': 'Backup'}</t>
+          <t>Backup</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'restore',_'label':_'restore',_'value':_'restore'}</t>
+          <t>restore</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Restore', 'label': 'Restore', 'value': 'Restore'}</t>
+          <t>Restore</t>
         </is>
       </c>
     </row>
